--- a/Metrics/Foremost/ninemost_EIGHT.xlsx
+++ b/Metrics/Foremost/ninemost_EIGHT.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sam\Desktop\2026 Y3 BIT\trimester2\Capstone\BHB-Capstone\Metrics\Foremost\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D54054E-D85D-40BA-83BE-0280C2EA2CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{446AE45A-7D92-4152-A7BF-426D87D7E25F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F5736CFC-DD2F-499C-8F1A-ED767B8B45E4}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F5736CFC-DD2F-499C-8F1A-ED767B8B45E4}"/>
   </bookViews>
   <sheets>
     <sheet name="ninemost_EIGHT_1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -617,7 +614,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -659,9 +656,6 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="16" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4127,27 +4121,27 @@
           </c:dLbls>
           <c:val>
             <c:numRef>
-              <c:f>ninemost_EIGHT_1!$H$106:$H$125</c:f>
+              <c:f>ninemost_EIGHT_1!$H$107:$H$125</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>35</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>36</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>39</c:v>
+                  <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>43</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>44</c:v>
@@ -4156,7 +4150,7 @@
                   <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>44</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>45</c:v>
@@ -4168,27 +4162,24 @@
                   <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>45</c:v>
+                  <c:v>46</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>46</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>42</c:v>
+                  <c:v>41</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>41</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="19">
                   <c:v>40</c:v>
                 </c:pt>
               </c:numCache>
@@ -18772,893 +18763,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="silentCartographer_soitNetworkS"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="B2" t="str">
-            <v xml:space="preserve"> memory.used [MiB]</v>
-          </cell>
-          <cell r="C2" t="str">
-            <v xml:space="preserve"> temperature.gpu</v>
-          </cell>
-          <cell r="D2" t="str">
-            <v xml:space="preserve"> power.draw [W]</v>
-          </cell>
-        </row>
-        <row r="169">
-          <cell r="B169">
-            <v>7066</v>
-          </cell>
-          <cell r="C169">
-            <v>27</v>
-          </cell>
-          <cell r="D169">
-            <v>5.95</v>
-          </cell>
-        </row>
-        <row r="170">
-          <cell r="B170">
-            <v>7066</v>
-          </cell>
-          <cell r="C170">
-            <v>27</v>
-          </cell>
-          <cell r="D170">
-            <v>5.92</v>
-          </cell>
-        </row>
-        <row r="171">
-          <cell r="B171">
-            <v>7066</v>
-          </cell>
-          <cell r="C171">
-            <v>27</v>
-          </cell>
-          <cell r="D171">
-            <v>5.93</v>
-          </cell>
-        </row>
-        <row r="172">
-          <cell r="B172">
-            <v>7066</v>
-          </cell>
-          <cell r="C172">
-            <v>27</v>
-          </cell>
-          <cell r="D172">
-            <v>5.93</v>
-          </cell>
-        </row>
-        <row r="173">
-          <cell r="B173">
-            <v>7066</v>
-          </cell>
-          <cell r="C173">
-            <v>27</v>
-          </cell>
-          <cell r="D173">
-            <v>6.01</v>
-          </cell>
-        </row>
-        <row r="174">
-          <cell r="B174">
-            <v>7066</v>
-          </cell>
-          <cell r="C174">
-            <v>27</v>
-          </cell>
-          <cell r="D174">
-            <v>6.07</v>
-          </cell>
-        </row>
-        <row r="175">
-          <cell r="B175">
-            <v>7066</v>
-          </cell>
-          <cell r="C175">
-            <v>27</v>
-          </cell>
-          <cell r="D175">
-            <v>6.01</v>
-          </cell>
-        </row>
-        <row r="176">
-          <cell r="B176">
-            <v>7066</v>
-          </cell>
-          <cell r="C176">
-            <v>26</v>
-          </cell>
-          <cell r="D176">
-            <v>5.96</v>
-          </cell>
-        </row>
-        <row r="177">
-          <cell r="B177">
-            <v>7066</v>
-          </cell>
-          <cell r="C177">
-            <v>26</v>
-          </cell>
-          <cell r="D177">
-            <v>5.95</v>
-          </cell>
-        </row>
-        <row r="178">
-          <cell r="B178">
-            <v>7066</v>
-          </cell>
-          <cell r="C178">
-            <v>26</v>
-          </cell>
-          <cell r="D178">
-            <v>5.96</v>
-          </cell>
-        </row>
-        <row r="179">
-          <cell r="B179">
-            <v>7066</v>
-          </cell>
-          <cell r="C179">
-            <v>28</v>
-          </cell>
-          <cell r="D179">
-            <v>13</v>
-          </cell>
-        </row>
-        <row r="180">
-          <cell r="B180">
-            <v>7066</v>
-          </cell>
-          <cell r="C180">
-            <v>29</v>
-          </cell>
-          <cell r="D180">
-            <v>52.26</v>
-          </cell>
-        </row>
-        <row r="181">
-          <cell r="B181">
-            <v>7066</v>
-          </cell>
-          <cell r="C181">
-            <v>29</v>
-          </cell>
-          <cell r="D181">
-            <v>54.26</v>
-          </cell>
-        </row>
-        <row r="182">
-          <cell r="B182">
-            <v>7066</v>
-          </cell>
-          <cell r="C182">
-            <v>30</v>
-          </cell>
-          <cell r="D182">
-            <v>54.12</v>
-          </cell>
-        </row>
-        <row r="183">
-          <cell r="B183">
-            <v>7066</v>
-          </cell>
-          <cell r="C183">
-            <v>30</v>
-          </cell>
-          <cell r="D183">
-            <v>54.26</v>
-          </cell>
-        </row>
-        <row r="184">
-          <cell r="B184">
-            <v>7066</v>
-          </cell>
-          <cell r="C184">
-            <v>30</v>
-          </cell>
-          <cell r="D184">
-            <v>54.15</v>
-          </cell>
-        </row>
-        <row r="185">
-          <cell r="B185">
-            <v>7066</v>
-          </cell>
-          <cell r="C185">
-            <v>30</v>
-          </cell>
-          <cell r="D185">
-            <v>54.21</v>
-          </cell>
-        </row>
-        <row r="186">
-          <cell r="B186">
-            <v>7066</v>
-          </cell>
-          <cell r="C186">
-            <v>30</v>
-          </cell>
-          <cell r="D186">
-            <v>54.66</v>
-          </cell>
-        </row>
-        <row r="187">
-          <cell r="B187">
-            <v>7066</v>
-          </cell>
-          <cell r="C187">
-            <v>30</v>
-          </cell>
-          <cell r="D187">
-            <v>54.41</v>
-          </cell>
-        </row>
-        <row r="188">
-          <cell r="B188">
-            <v>7066</v>
-          </cell>
-          <cell r="C188">
-            <v>30</v>
-          </cell>
-          <cell r="D188">
-            <v>54.37</v>
-          </cell>
-        </row>
-        <row r="189">
-          <cell r="B189">
-            <v>7066</v>
-          </cell>
-          <cell r="C189">
-            <v>31</v>
-          </cell>
-          <cell r="D189">
-            <v>54.63</v>
-          </cell>
-        </row>
-        <row r="190">
-          <cell r="B190">
-            <v>7066</v>
-          </cell>
-          <cell r="C190">
-            <v>31</v>
-          </cell>
-          <cell r="D190">
-            <v>54.78</v>
-          </cell>
-        </row>
-        <row r="191">
-          <cell r="B191">
-            <v>7066</v>
-          </cell>
-          <cell r="C191">
-            <v>31</v>
-          </cell>
-          <cell r="D191">
-            <v>54.64</v>
-          </cell>
-        </row>
-        <row r="192">
-          <cell r="B192">
-            <v>7066</v>
-          </cell>
-          <cell r="C192">
-            <v>31</v>
-          </cell>
-          <cell r="D192">
-            <v>54.78</v>
-          </cell>
-        </row>
-        <row r="193">
-          <cell r="B193">
-            <v>7066</v>
-          </cell>
-          <cell r="C193">
-            <v>31</v>
-          </cell>
-          <cell r="D193">
-            <v>54.75</v>
-          </cell>
-        </row>
-        <row r="194">
-          <cell r="B194">
-            <v>7066</v>
-          </cell>
-          <cell r="C194">
-            <v>31</v>
-          </cell>
-          <cell r="D194">
-            <v>54.72</v>
-          </cell>
-        </row>
-        <row r="195">
-          <cell r="B195">
-            <v>7066</v>
-          </cell>
-          <cell r="C195">
-            <v>31</v>
-          </cell>
-          <cell r="D195">
-            <v>55</v>
-          </cell>
-        </row>
-        <row r="196">
-          <cell r="B196">
-            <v>7066</v>
-          </cell>
-          <cell r="C196">
-            <v>31</v>
-          </cell>
-          <cell r="D196">
-            <v>54.75</v>
-          </cell>
-        </row>
-        <row r="197">
-          <cell r="B197">
-            <v>7066</v>
-          </cell>
-          <cell r="C197">
-            <v>31</v>
-          </cell>
-          <cell r="D197">
-            <v>54.81</v>
-          </cell>
-        </row>
-        <row r="198">
-          <cell r="B198">
-            <v>7066</v>
-          </cell>
-          <cell r="C198">
-            <v>31</v>
-          </cell>
-          <cell r="D198">
-            <v>52.68</v>
-          </cell>
-        </row>
-        <row r="199">
-          <cell r="B199">
-            <v>7066</v>
-          </cell>
-          <cell r="C199">
-            <v>32</v>
-          </cell>
-          <cell r="D199">
-            <v>48.81</v>
-          </cell>
-        </row>
-        <row r="200">
-          <cell r="B200">
-            <v>7066</v>
-          </cell>
-          <cell r="C200">
-            <v>33</v>
-          </cell>
-          <cell r="D200">
-            <v>71.849999999999994</v>
-          </cell>
-        </row>
-        <row r="201">
-          <cell r="B201">
-            <v>7066</v>
-          </cell>
-          <cell r="C201">
-            <v>32</v>
-          </cell>
-          <cell r="D201">
-            <v>65.959999999999994</v>
-          </cell>
-        </row>
-        <row r="202">
-          <cell r="B202">
-            <v>7066</v>
-          </cell>
-          <cell r="C202">
-            <v>32</v>
-          </cell>
-          <cell r="D202">
-            <v>54.71</v>
-          </cell>
-        </row>
-        <row r="203">
-          <cell r="B203">
-            <v>7066</v>
-          </cell>
-          <cell r="C203">
-            <v>33</v>
-          </cell>
-          <cell r="D203">
-            <v>59.38</v>
-          </cell>
-        </row>
-        <row r="204">
-          <cell r="B204">
-            <v>7066</v>
-          </cell>
-          <cell r="C204">
-            <v>34</v>
-          </cell>
-          <cell r="D204">
-            <v>66.819999999999993</v>
-          </cell>
-        </row>
-        <row r="205">
-          <cell r="B205">
-            <v>7066</v>
-          </cell>
-          <cell r="C205">
-            <v>34</v>
-          </cell>
-          <cell r="D205">
-            <v>72.72</v>
-          </cell>
-        </row>
-        <row r="206">
-          <cell r="B206">
-            <v>7066</v>
-          </cell>
-          <cell r="C206">
-            <v>33</v>
-          </cell>
-          <cell r="D206">
-            <v>60.28</v>
-          </cell>
-        </row>
-        <row r="207">
-          <cell r="B207">
-            <v>7066</v>
-          </cell>
-          <cell r="C207">
-            <v>33</v>
-          </cell>
-          <cell r="D207">
-            <v>55.52</v>
-          </cell>
-        </row>
-        <row r="208">
-          <cell r="B208">
-            <v>7066</v>
-          </cell>
-          <cell r="C208">
-            <v>33</v>
-          </cell>
-          <cell r="D208">
-            <v>55.51</v>
-          </cell>
-        </row>
-        <row r="209">
-          <cell r="B209">
-            <v>7066</v>
-          </cell>
-          <cell r="C209">
-            <v>33</v>
-          </cell>
-          <cell r="D209">
-            <v>55.51</v>
-          </cell>
-        </row>
-        <row r="210">
-          <cell r="B210">
-            <v>7066</v>
-          </cell>
-          <cell r="C210">
-            <v>33</v>
-          </cell>
-          <cell r="D210">
-            <v>55.31</v>
-          </cell>
-        </row>
-        <row r="211">
-          <cell r="B211">
-            <v>7066</v>
-          </cell>
-          <cell r="C211">
-            <v>33</v>
-          </cell>
-          <cell r="D211">
-            <v>55.45</v>
-          </cell>
-        </row>
-        <row r="212">
-          <cell r="B212">
-            <v>7066</v>
-          </cell>
-          <cell r="C212">
-            <v>33</v>
-          </cell>
-          <cell r="D212">
-            <v>55.58</v>
-          </cell>
-        </row>
-        <row r="213">
-          <cell r="B213">
-            <v>7066</v>
-          </cell>
-          <cell r="C213">
-            <v>33</v>
-          </cell>
-          <cell r="D213">
-            <v>55.42</v>
-          </cell>
-        </row>
-        <row r="214">
-          <cell r="B214">
-            <v>7066</v>
-          </cell>
-          <cell r="C214">
-            <v>33</v>
-          </cell>
-          <cell r="D214">
-            <v>55.22</v>
-          </cell>
-        </row>
-        <row r="215">
-          <cell r="B215">
-            <v>7066</v>
-          </cell>
-          <cell r="C215">
-            <v>33</v>
-          </cell>
-          <cell r="D215">
-            <v>55.48</v>
-          </cell>
-        </row>
-        <row r="216">
-          <cell r="B216">
-            <v>7066</v>
-          </cell>
-          <cell r="C216">
-            <v>34</v>
-          </cell>
-          <cell r="D216">
-            <v>55.24</v>
-          </cell>
-        </row>
-        <row r="217">
-          <cell r="B217">
-            <v>7066</v>
-          </cell>
-          <cell r="C217">
-            <v>34</v>
-          </cell>
-          <cell r="D217">
-            <v>55.55</v>
-          </cell>
-        </row>
-        <row r="218">
-          <cell r="B218">
-            <v>7066</v>
-          </cell>
-          <cell r="C218">
-            <v>34</v>
-          </cell>
-          <cell r="D218">
-            <v>55.46</v>
-          </cell>
-        </row>
-        <row r="219">
-          <cell r="B219">
-            <v>7066</v>
-          </cell>
-          <cell r="C219">
-            <v>34</v>
-          </cell>
-          <cell r="D219">
-            <v>55.38</v>
-          </cell>
-        </row>
-        <row r="220">
-          <cell r="B220">
-            <v>7066</v>
-          </cell>
-          <cell r="C220">
-            <v>33</v>
-          </cell>
-          <cell r="D220">
-            <v>47.17</v>
-          </cell>
-        </row>
-        <row r="221">
-          <cell r="B221">
-            <v>7066</v>
-          </cell>
-          <cell r="C221">
-            <v>33</v>
-          </cell>
-          <cell r="D221">
-            <v>40.81</v>
-          </cell>
-        </row>
-        <row r="222">
-          <cell r="B222">
-            <v>7066</v>
-          </cell>
-          <cell r="C222">
-            <v>33</v>
-          </cell>
-          <cell r="D222">
-            <v>37.85</v>
-          </cell>
-        </row>
-        <row r="223">
-          <cell r="B223">
-            <v>7066</v>
-          </cell>
-          <cell r="C223">
-            <v>33</v>
-          </cell>
-          <cell r="D223">
-            <v>37.82</v>
-          </cell>
-        </row>
-        <row r="224">
-          <cell r="B224">
-            <v>7066</v>
-          </cell>
-          <cell r="C224">
-            <v>33</v>
-          </cell>
-          <cell r="D224">
-            <v>37.81</v>
-          </cell>
-        </row>
-        <row r="225">
-          <cell r="B225">
-            <v>7066</v>
-          </cell>
-          <cell r="C225">
-            <v>32</v>
-          </cell>
-          <cell r="D225">
-            <v>37.840000000000003</v>
-          </cell>
-        </row>
-        <row r="226">
-          <cell r="B226">
-            <v>7066</v>
-          </cell>
-          <cell r="C226">
-            <v>33</v>
-          </cell>
-          <cell r="D226">
-            <v>37.75</v>
-          </cell>
-        </row>
-        <row r="227">
-          <cell r="B227">
-            <v>7066</v>
-          </cell>
-          <cell r="C227">
-            <v>33</v>
-          </cell>
-          <cell r="D227">
-            <v>37.619999999999997</v>
-          </cell>
-        </row>
-        <row r="228">
-          <cell r="B228">
-            <v>7066</v>
-          </cell>
-          <cell r="C228">
-            <v>33</v>
-          </cell>
-          <cell r="D228">
-            <v>37.6</v>
-          </cell>
-        </row>
-        <row r="229">
-          <cell r="B229">
-            <v>7066</v>
-          </cell>
-          <cell r="C229">
-            <v>33</v>
-          </cell>
-          <cell r="D229">
-            <v>37.659999999999997</v>
-          </cell>
-        </row>
-        <row r="230">
-          <cell r="B230">
-            <v>7066</v>
-          </cell>
-          <cell r="C230">
-            <v>32</v>
-          </cell>
-          <cell r="D230">
-            <v>37.76</v>
-          </cell>
-        </row>
-        <row r="231">
-          <cell r="B231">
-            <v>7066</v>
-          </cell>
-          <cell r="C231">
-            <v>33</v>
-          </cell>
-          <cell r="D231">
-            <v>37.78</v>
-          </cell>
-        </row>
-        <row r="232">
-          <cell r="B232">
-            <v>7066</v>
-          </cell>
-          <cell r="C232">
-            <v>32</v>
-          </cell>
-          <cell r="D232">
-            <v>37.78</v>
-          </cell>
-        </row>
-        <row r="233">
-          <cell r="B233">
-            <v>7066</v>
-          </cell>
-          <cell r="C233">
-            <v>33</v>
-          </cell>
-          <cell r="D233">
-            <v>37.78</v>
-          </cell>
-        </row>
-        <row r="234">
-          <cell r="B234">
-            <v>7066</v>
-          </cell>
-          <cell r="C234">
-            <v>33</v>
-          </cell>
-          <cell r="D234">
-            <v>37.79</v>
-          </cell>
-        </row>
-        <row r="235">
-          <cell r="B235">
-            <v>7066</v>
-          </cell>
-          <cell r="C235">
-            <v>32</v>
-          </cell>
-          <cell r="D235">
-            <v>37.76</v>
-          </cell>
-        </row>
-        <row r="236">
-          <cell r="B236">
-            <v>7066</v>
-          </cell>
-          <cell r="C236">
-            <v>32</v>
-          </cell>
-          <cell r="D236">
-            <v>37.67</v>
-          </cell>
-        </row>
-        <row r="237">
-          <cell r="B237">
-            <v>7066</v>
-          </cell>
-          <cell r="C237">
-            <v>31</v>
-          </cell>
-          <cell r="D237">
-            <v>29.47</v>
-          </cell>
-        </row>
-        <row r="238">
-          <cell r="B238">
-            <v>7066</v>
-          </cell>
-          <cell r="C238">
-            <v>31</v>
-          </cell>
-          <cell r="D238">
-            <v>19.420000000000002</v>
-          </cell>
-        </row>
-        <row r="239">
-          <cell r="B239">
-            <v>7066</v>
-          </cell>
-          <cell r="C239">
-            <v>31</v>
-          </cell>
-          <cell r="D239">
-            <v>7.84</v>
-          </cell>
-        </row>
-        <row r="240">
-          <cell r="B240">
-            <v>7066</v>
-          </cell>
-          <cell r="C240">
-            <v>31</v>
-          </cell>
-          <cell r="D240">
-            <v>6.28</v>
-          </cell>
-        </row>
-        <row r="241">
-          <cell r="B241">
-            <v>7066</v>
-          </cell>
-          <cell r="C241">
-            <v>30</v>
-          </cell>
-          <cell r="D241">
-            <v>6.23</v>
-          </cell>
-        </row>
-        <row r="242">
-          <cell r="B242">
-            <v>7066</v>
-          </cell>
-          <cell r="C242">
-            <v>30</v>
-          </cell>
-          <cell r="D242">
-            <v>6.14</v>
-          </cell>
-        </row>
-        <row r="243">
-          <cell r="B243">
-            <v>7066</v>
-          </cell>
-          <cell r="C243">
-            <v>30</v>
-          </cell>
-          <cell r="D243">
-            <v>6.09</v>
-          </cell>
-        </row>
-        <row r="244">
-          <cell r="B244">
-            <v>7066</v>
-          </cell>
-          <cell r="C244">
-            <v>30</v>
-          </cell>
-          <cell r="D244">
-            <v>6.15</v>
-          </cell>
-        </row>
-        <row r="245">
-          <cell r="B245">
-            <v>7066</v>
-          </cell>
-          <cell r="C245">
-            <v>30</v>
-          </cell>
-          <cell r="D245">
-            <v>6.16</v>
-          </cell>
-        </row>
-        <row r="246">
-          <cell r="B246">
-            <v>7066</v>
-          </cell>
-          <cell r="C246">
-            <v>30</v>
-          </cell>
-          <cell r="D246">
-            <v>6.05</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -20955,9 +20059,9 @@
       <c r="A105" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B105" s="17"/>
-      <c r="C105" s="17"/>
-      <c r="D105" s="17"/>
+      <c r="B105" s="4"/>
+      <c r="C105" s="4"/>
+      <c r="D105" s="4"/>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
